--- a/data/analysis/research_aggregates.xlsx
+++ b/data/analysis/research_aggregates.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:Z46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,17 +1709,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12_SYED_TAMOORULHASSAN</t>
+          <t>09_SANA_FATIMA_RIZVI</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -1743,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1764,16 +1764,16 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>The candidate has 7 publication(s) in total (3 journal, 4 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 3 publication(s) in total (3 journal, 0 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1797,74 +1797,74 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13_MANZOOR_ELLAHI</t>
+          <t>12_SYED_TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>9</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
       <c r="W16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>The candidate has 23 publication(s) in total (13 journal, 10 conference). 3 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 7 publication(s) in total (3 journal, 4 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1885,74 +1885,74 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14_SAROSH_TAHIR</t>
+          <t>13_MANZOOR_ELLAHI</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" t="n">
         <v>8</v>
       </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>The candidate has 10 publication(s) in total (2 journal, 8 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 23 publication(s) in total (13 journal, 10 conference). 3 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -1973,41 +1973,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>14_SAROSH_TAHIR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>The candidate has 6 publication(s) in total (3 journal, 3 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 10 publication(s) in total (2 journal, 8 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2061,74 +2061,74 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17_SUHAIL_ASGHAR</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
         <v>6</v>
       </c>
-      <c r="E19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>The candidate has 8 publication(s) in total (8 journal, 0 conference). 6 paper(s) are in Q1/Q2 Scopus-ranked journals. 6 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 6 publication(s) in total (3 journal, 3 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2149,45 +2149,45 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19_ASIM_MASOOD</t>
+          <t>17_SUHAIL_ASGHAR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="n">
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>2</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2204,19 +2204,19 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>The candidate has 8 publication(s) in total (5 journal, 3 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 8 publication(s) in total (8 journal, 0 conference). 6 paper(s) are in Q1/Q2 Scopus-ranked journals. 6 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2237,54 +2237,54 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20_SYED_FASIH_ALI</t>
+          <t>19_ASIM_MASOOD</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
         <v>3</v>
       </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>2</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
@@ -2292,16 +2292,16 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>The candidate has 4 publication(s) in total (3 journal, 1 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 8 publication(s) in total (5 journal, 3 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2325,71 +2325,71 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22_ZEESHAN</t>
+          <t>20_SYED_FASIH_ALI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>5</v>
-      </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>The candidate has 10 publication(s) in total (8 journal, 2 conference). 4 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 4 publication(s) in total (3 journal, 1 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -2413,44 +2413,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24_AHMED_NAEEM</t>
+          <t>22_ZEESHAN</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
         <v>7</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2471,13 +2471,13 @@
         <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>The candidate has 11 publication(s) in total (7 journal, 4 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 10 publication(s) in total (8 journal, 2 conference). 4 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -2501,53 +2501,53 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>24_AHMED_NAEEM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2559,14 +2559,14 @@
         <v>2</v>
       </c>
       <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
         <v>5</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>The candidate has 5 publication(s) in total (3 journal, 2 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 11 publication(s) in total (7 journal, 4 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -2589,71 +2589,71 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28_IDRIS_KHAN</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
         <v>5</v>
       </c>
-      <c r="C25" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>The candidate has 10 publication(s) in total (5 journal, 5 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 5 publication(s) in total (3 journal, 2 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -2677,72 +2677,72 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
+          <t>28_IDRIS_KHAN</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>3</v>
       </c>
-      <c r="C26" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>4</v>
       </c>
-      <c r="D26" t="n">
+      <c r="T26" t="n">
         <v>3</v>
       </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
         <v>7</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>The candidate has 7 publication(s) in total (3 journal, 4 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 10 publication(s) in total (5 journal, 5 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -2765,21 +2765,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30_FAHD_SIKANDAR_KHAN</t>
+          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
         <v>2</v>
       </c>
-      <c r="D27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
@@ -2787,34 +2787,34 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>The candidate has 9 publication(s) in total (7 journal, 2 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 7 publication(s) in total (3 journal, 4 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -2853,44 +2853,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>31_USMAN_MASUD</t>
+          <t>30_FAHD_SIKANDAR_KHAN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2908,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>The candidate has 3 publication(s) in total (3 journal, 0 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 9 publication(s) in total (7 journal, 2 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -2941,38 +2941,38 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>32_QAISAR_HUSSAIN_ALVI</t>
+          <t>31_USMAN_MASUD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>The candidate has 4 publication(s) in total (4 journal, 0 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 3 publication(s) in total (3 journal, 0 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3029,44 +3029,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>33_QAMAR_ABBAS</t>
+          <t>32_QAISAR_HUSSAIN_ALVI</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
       <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>2</v>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -3084,19 +3084,19 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>The candidate has 7 publication(s) in total (5 journal, 2 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 4 publication(s) in total (4 journal, 0 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3117,14 +3117,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>35_MATIULLAH_AHSAN</t>
+          <t>33_QAMAR_ABBAS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
@@ -3133,10 +3133,10 @@
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3154,35 +3154,35 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
         <v>2</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>The candidate has 5 publication(s) in total (4 journal, 1 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 7 publication(s) in total (5 journal, 2 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -3205,44 +3205,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>36_SAMANA_BATOOL</t>
+          <t>35_MATIULLAH_AHSAN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3260,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>The candidate has 3 publication(s) in total (3 journal, 0 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
+          <t>The candidate has 5 publication(s) in total (4 journal, 1 conference). 2 paper(s) are in Q1/Q2 Scopus-ranked journals. 2 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -3293,44 +3293,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01_MUHAMMAD_SALMAN</t>
+          <t>36_SAMANA_BATOOL</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -3348,10 +3348,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3364,34 +3364,34 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>The candidate has 5 publication(s) in total (4 journal, 1 conference). Overall research profile is assessed as Weak.</t>
+          <t>The candidate has 3 publication(s) in total (3 journal, 0 conference). 1 paper(s) are in Q1/Q2 Scopus-ranked journals. 1 paper(s) are indexed in Web of Science. Overall research profile is assessed as Moderate.</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05_MUHAMMAD_MAJID</t>
+          <t>01_MUHAMMAD_SALMAN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -3415,10 +3415,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>The candidate has 3 publication(s) in total (2 journal, 1 conference). Overall research profile is assessed as Weak.</t>
+          <t>The candidate has 5 publication(s) in total (4 journal, 1 conference). Overall research profile is assessed as Weak.</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -3469,17 +3469,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08_TAYYABA_GULL</t>
+          <t>05_MUHAMMAD_MAJID</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -3524,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>The candidate has 5 publication(s) in total (5 journal, 0 conference). Overall research profile is assessed as Weak.</t>
+          <t>The candidate has 3 publication(s) in total (2 journal, 1 conference). Overall research profile is assessed as Weak.</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -3557,17 +3557,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21_SAMAN_FATIMA</t>
+          <t>08_TAYYABA_GULL</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3591,10 +3591,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3612,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>The candidate has 1 publication(s) in total (0 journal, 1 conference). Overall research profile is assessed as Weak.</t>
+          <t>The candidate has 5 publication(s) in total (5 journal, 0 conference). Overall research profile is assessed as Weak.</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -3645,17 +3645,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>26_AAMINA_AKBAR</t>
+          <t>21_SAMAN_FATIMA</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -3703,13 +3703,13 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>The candidate has 4 publication(s) in total (3 journal, 1 conference). Overall research profile is assessed as Weak.</t>
+          <t>The candidate has 1 publication(s) in total (0 journal, 1 conference). Overall research profile is assessed as Weak.</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -3733,17 +3733,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>39_MUHAMMAD_SAQIB</t>
+          <t>26_AAMINA_AKBAR</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3767,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3788,16 +3788,16 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>The candidate has 17 publication(s) in total (17 journal, 0 conference). Overall research profile is assessed as Weak.</t>
+          <t>The candidate has 4 publication(s) in total (3 journal, 1 conference). Overall research profile is assessed as Weak.</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -3821,14 +3821,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40_ABDUR_REHMAN</t>
+          <t>39_MUHAMMAD_SAQIB</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3855,10 +3855,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>The candidate has 5 publication(s) in total (2 journal, 3 conference). Overall research profile is assessed as Weak.</t>
+          <t>The candidate has 17 publication(s) in total (17 journal, 0 conference). Overall research profile is assessed as Weak.</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -3909,14 +3909,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>02_MUHAMMAD_SHAHWAZ</t>
+          <t>40_ABDUR_REHMAN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -3943,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3980,24 +3980,24 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Needs Clarification</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>The candidate has no publication records in the dataset.</t>
+          <t>The candidate has 5 publication(s) in total (2 journal, 3 conference). Overall research profile is assessed as Weak.</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Needs Clarification</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06_FARMAN_ALI</t>
+          <t>02_MUHAMMAD_SHAHWAZ</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -4085,7 +4085,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>06_FARMAN_ALI</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -4173,7 +4173,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -4261,86 +4261,262 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>27_SHAHEER</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>The candidate has no publication records in the dataset.</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>42_SAQIB_JAMIL</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="inlineStr">
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="inlineStr">
         <is>
           <t>Needs Clarification</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>The candidate has no publication records in the dataset.</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>The candidate has no publication records in the dataset.</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
         <is>
           <t>Needs Clarification</t>
         </is>
@@ -4357,7 +4533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q280"/>
+  <dimension ref="A1:Q283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21880,7 +22056,7 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -21943,7 +22119,7 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -22010,7 +22186,7 @@
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -22073,7 +22249,7 @@
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -22136,7 +22312,7 @@
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -22203,7 +22379,7 @@
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -22272,7 +22448,7 @@
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -22341,7 +22517,7 @@
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -22408,7 +22584,7 @@
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -22475,7 +22651,7 @@
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -22544,7 +22720,7 @@
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -22607,7 +22783,7 @@
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -22670,7 +22846,7 @@
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -22733,7 +22909,7 @@
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -22802,7 +22978,7 @@
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -22871,7 +23047,7 @@
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -22940,7 +23116,7 @@
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -22979,6 +23155,203 @@
       <c r="Q280" t="inlineStr">
         <is>
           <t>MISSING_DOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Transformer-Based Sentiment Analysis for Low-Resource Urdu Text</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E281" t="b">
+        <v>0</v>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2024.0</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Sana Fatima Rizvi, Ahmad Raza, Bilal Yousaf</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="b">
+        <v>1</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="L281" t="b">
+        <v>1</v>
+      </c>
+      <c r="M281" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N281" t="b">
+        <v>0</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>First Author</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>High Impact</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>MISSING_DOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>A Federated Learning Framework for Privacy-Preserving Healthcare Diagnostics</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="E282" t="b">
+        <v>0</v>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2023.0</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Sana Fatima Rizvi, Ahmad Raza, ...</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="b">
+        <v>1</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="L282" t="b">
+        <v>1</v>
+      </c>
+      <c r="M282" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N282" t="b">
+        <v>0</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>First Author</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>High Impact</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>MISSING_DOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Deep Learning Approaches for Crop Disease Detection in Punjab Informatics &amp; Biomedical</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Journal of Computing</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Journal of Computing</t>
+        </is>
+      </c>
+      <c r="E283" t="b">
+        <v>0</v>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2022.0</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Sana Fatima Rizvi, Hina Malik, Ahmad Raza, ...</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="b">
+        <v>0</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>First Author</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Unverified Venue</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>VENUE_UNVERIFIABLE | MISSING_DOI</t>
         </is>
       </c>
     </row>
